--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890E1668-BF89-4B99-9E54-890A9D3E801C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A294558-35FF-4AB8-A207-75D0913DF47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10060" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -632,7 +632,7 @@
         <v>19</v>
       </c>
       <c r="C6" s="3">
-        <v>1.1000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -646,7 +646,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="3">
-        <v>1.1000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -674,7 +674,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -688,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -702,7 +702,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -716,7 +716,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -730,7 +730,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -744,7 +744,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -772,7 +772,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A294558-35FF-4AB8-A207-75D0913DF47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C71C839-4667-4961-AC58-14A76447CACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10060" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -134,10 +134,6 @@
   </si>
   <si>
     <t>실력</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -626,24 +622,24 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>18</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="C6" s="3">
         <v>1.5</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C7" s="3">
         <v>1.5</v>
@@ -654,24 +650,24 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>4</v>
+        <v>18</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C8" s="3">
         <v>1.5</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
         <v>1.5</v>
@@ -724,15 +720,15 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>22</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>23</v>
+        <v>7</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C13" s="3">
         <v>2.5</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>1</v>
       </c>
     </row>
@@ -752,15 +748,15 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>7</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>1</v>
       </c>
     </row>
@@ -808,13 +804,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" s="4">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D19" s="4">
         <v>2</v>
@@ -822,10 +818,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C20" s="4">
         <v>2</v>
@@ -856,7 +852,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="4">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="D22" s="4">
         <v>2</v>
@@ -869,8 +865,8 @@
       <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>26</v>
+      <c r="C23" s="3">
+        <v>3.5</v>
       </c>
       <c r="D23" s="3">
         <v>2</v>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C71C839-4667-4961-AC58-14A76447CACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC0E329-F54E-4A32-8FD5-27FD5BB8C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10060" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -734,29 +734,29 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>6</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>7</v>
+        <v>22</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C14" s="3">
         <v>2.5</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>22</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>23</v>
+        <v>6</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>1</v>
       </c>
     </row>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC0E329-F54E-4A32-8FD5-27FD5BB8C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CC85E2-186C-44F4-B13F-4CA307B5C593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,38 +566,38 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>19</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="B2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>20</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -608,13 +608,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -636,41 +636,41 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C7" s="3">
         <v>1.5</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="C8" s="3">
         <v>1.5</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C9" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3">
         <v>2</v>
@@ -804,10 +804,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C19" s="4">
         <v>1.5</v>
@@ -818,13 +818,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C20" s="4">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D20" s="4">
         <v>2</v>
@@ -838,7 +838,7 @@
         <v>13</v>
       </c>
       <c r="C21" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="4">
         <v>2</v>
@@ -852,7 +852,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D22" s="4">
         <v>2</v>
@@ -866,7 +866,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="3">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D23" s="3">
         <v>2</v>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CC85E2-186C-44F4-B13F-4CA307B5C593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFF739DE-B9FD-442F-A40B-D937D87C7566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -636,41 +636,41 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>18</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="C7" s="3">
         <v>1.5</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="s">
         <v>18</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C8" s="3">
         <v>1.5</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -678,10 +678,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3">
         <v>2</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="C13" s="3">
         <v>2.5</v>
@@ -734,29 +734,29 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>22</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>23</v>
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C14" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>6</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>7</v>
+        <v>22</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>1</v>
       </c>
     </row>
@@ -776,38 +776,38 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>21</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3">
+        <v>12</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>12</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4">
+        <v>21</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D18" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" s="4">
         <v>1.5</v>
@@ -818,13 +818,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C20" s="4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="4">
         <v>2</v>
@@ -832,15 +832,15 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>14</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="4">
-        <v>2</v>
-      </c>
-      <c r="D21" s="4">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D21" s="3">
         <v>2</v>
       </c>
     </row>
@@ -860,15 +860,15 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>8</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="3">
+        <v>14</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="4">
         <v>3</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="4">
         <v>2</v>
       </c>
     </row>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFF739DE-B9FD-442F-A40B-D937D87C7566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F616BB7-7673-4023-8E34-14DA53D9D183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5250" yWindow="3090" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -134,6 +134,30 @@
   </si>
   <si>
     <t>실력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -173,7 +197,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -196,68 +220,23 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -543,10 +522,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="5" customWidth="1"/>
     <col min="3" max="4" width="36.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -554,321 +533,401 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>20</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="4">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="1">
         <v>1.5</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="1">
         <v>1.5</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1">
         <v>1.5</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>18</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <v>1.5</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="1">
         <v>1.5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="3">
-        <v>2</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>13</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="3">
-        <v>2</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>6</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="1">
         <v>2.5</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>7</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="1">
         <v>3</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>22</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="1">
         <v>3</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>4</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="1">
         <v>3</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>12</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4">
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>21</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>1.5</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>9</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="2">
         <v>1.5</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>11</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="4">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4">
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>8</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="1">
         <v>2.5</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>16</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="2">
         <v>3</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="A23" s="1">
         <v>14</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="2">
         <v>3</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="3">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="3">
+        <v>3</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4">
         <v>2</v>
       </c>
     </row>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F616BB7-7673-4023-8E34-14DA53D9D183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3E910B-AC64-4A97-8ECD-F3C41A602E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5250" yWindow="3090" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,27 +137,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>남1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>여3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김양우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양현철</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박종운</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종운동생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민규</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -233,9 +233,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -525,7 +522,7 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.25" style="5" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="4" customWidth="1"/>
     <col min="3" max="4" width="36.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -677,10 +674,10 @@
         <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -705,10 +702,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="1">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -719,10 +716,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -856,12 +853,12 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="2">
         <v>1</v>
       </c>
     </row>
@@ -870,12 +867,12 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
         <v>1</v>
       </c>
     </row>
@@ -884,10 +881,12 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4">
+        <v>29</v>
+      </c>
+      <c r="C26" s="3">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2">
         <v>1</v>
       </c>
     </row>
@@ -896,13 +895,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
       </c>
-      <c r="D27" s="4">
-        <v>2</v>
+      <c r="D27" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -910,13 +909,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C28" s="3">
-        <v>3</v>
-      </c>
-      <c r="D28" s="4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -924,10 +923,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C29" s="3"/>
-      <c r="D29" s="4">
+      <c r="D29" s="2">
         <v>2</v>
       </c>
     </row>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3E910B-AC64-4A97-8ECD-F3C41A602E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C79FFFC-2918-49D3-B627-4491E8BDD5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -716,7 +716,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
@@ -744,10 +744,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C79FFFC-2918-49D3-B627-4491E8BDD5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4041539B-BED8-4EA7-A064-CD60CDD17A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -674,10 +674,10 @@
         <v>15</v>
       </c>
       <c r="C11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -702,10 +702,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -716,10 +716,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -730,7 +730,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -744,10 +744,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4041539B-BED8-4EA7-A064-CD60CDD17A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94094AA4-6744-42B3-96EB-C356433BE904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -158,6 +158,10 @@
   </si>
   <si>
     <t>민규</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초지원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -519,7 +523,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" style="4" customWidth="1"/>
@@ -849,25 +853,21 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="3">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2">
-        <v>1</v>
-      </c>
+      <c r="B24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3">
         <v>1</v>
@@ -881,10 +881,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -895,10 +895,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -909,7 +909,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -923,10 +923,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="2">
+      <c r="C30" s="3"/>
+      <c r="D30" s="2">
         <v>2</v>
       </c>
     </row>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94094AA4-6744-42B3-96EB-C356433BE904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD69AAB8-00D0-4404-85A7-F0D6583744D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -161,7 +161,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>초지원</t>
+    <t>최지원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -859,8 +859,12 @@
       <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD69AAB8-00D0-4404-85A7-F0D6583744D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CADBFEC-C600-4E8C-9CF9-5FDE2F831B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -141,27 +141,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>김양우</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>양현철</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박종운</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>종운동생</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>민규</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>최지원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -857,7 +857,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C24" s="2">
         <v>2</v>
@@ -871,7 +871,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3">
         <v>1</v>
@@ -885,10 +885,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
@@ -899,7 +899,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="3">
         <v>3</v>
@@ -913,13 +913,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
       </c>
       <c r="D28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -927,13 +927,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -943,7 +943,9 @@
       <c r="B30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="3"/>
+      <c r="C30" s="3">
+        <v>3</v>
+      </c>
       <c r="D30" s="2">
         <v>2</v>
       </c>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CADBFEC-C600-4E8C-9CF9-5FDE2F831B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD32A49-B790-4C9B-A304-CE43286F6B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4845" yWindow="465" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,10 +69,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>카밀라</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>정준섭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,6 +159,9 @@
   <si>
     <t>여2</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>까밀라</t>
   </si>
 </sst>
 </file>
@@ -538,10 +537,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -549,7 +548,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -563,7 +562,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -591,7 +590,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1">
         <v>1.5</v>
@@ -633,7 +632,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1">
         <v>1.5</v>
@@ -647,7 +646,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>1.5</v>
@@ -675,7 +674,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
         <v>2</v>
@@ -689,7 +688,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1">
         <v>2</v>
@@ -731,7 +730,7 @@
         <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1">
         <v>2.5</v>
@@ -759,7 +758,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -773,7 +772,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1">
         <v>1.5</v>
@@ -787,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C19" s="2">
         <v>1.5</v>
@@ -801,7 +800,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
@@ -815,7 +814,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" s="1">
         <v>2.5</v>
@@ -829,7 +828,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
@@ -843,7 +842,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
@@ -857,7 +856,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="2">
         <v>2</v>
@@ -871,7 +870,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3">
         <v>1</v>
@@ -885,7 +884,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="3">
         <v>2</v>
@@ -899,7 +898,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" s="3">
         <v>3</v>
@@ -913,7 +912,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -927,7 +926,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="3">
         <v>2</v>
@@ -941,7 +940,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C30" s="3">
         <v>3</v>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD32A49-B790-4C9B-A304-CE43286F6B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369DD87B-1D1E-48D6-9E24-D4AD9E3EDD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4845" yWindow="465" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -133,35 +133,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>여3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>최지원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>남1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>까밀라</t>
+  </si>
+  <si>
+    <t>남1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남3.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남3.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여3.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여3.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -227,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -237,6 +261,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -522,7 +553,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" style="4" customWidth="1"/>
@@ -786,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C19" s="2">
         <v>1.5</v>
@@ -856,7 +887,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" s="2">
         <v>2</v>
@@ -866,7 +897,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -880,72 +911,156 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+      <c r="A30" s="5">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C30" s="3">
         <v>3</v>
       </c>
       <c r="D30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="6">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3</v>
+      </c>
+      <c r="D36" s="7">
         <v>2</v>
       </c>
     </row>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369DD87B-1D1E-48D6-9E24-D4AD9E3EDD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAE418E-3503-4C30-8020-27C6CDA8FAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -251,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -265,10 +265,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -932,7 +928,7 @@
         <v>29</v>
       </c>
       <c r="C27" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2">
         <v>1</v>
@@ -1029,10 +1025,10 @@
       <c r="B34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="6">
-        <v>2</v>
-      </c>
-      <c r="D34" s="7">
+      <c r="C34" s="3">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2">
         <v>2</v>
       </c>
     </row>
@@ -1043,10 +1039,10 @@
       <c r="B35" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="3">
         <v>3</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="2">
         <v>2</v>
       </c>
     </row>
@@ -1057,10 +1053,10 @@
       <c r="B36" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="3">
         <v>3</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="2">
         <v>2</v>
       </c>
     </row>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAE418E-3503-4C30-8020-27C6CDA8FAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F33439-B736-400F-B45D-89AB7A7326C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,22 +140,10 @@
     <t>까밀라</t>
   </si>
   <si>
-    <t>남1.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>남1.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>남2.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남2.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>남3.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -164,10 +152,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>여1.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>여1.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,11 +164,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>여3.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>여3.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이휘영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>까미게스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박수현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수현남편님</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김예진</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -897,7 +897,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C25" s="3">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -925,7 +925,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3">
         <v>2</v>
@@ -953,7 +953,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C29" s="3">
         <v>3</v>
@@ -967,7 +967,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C30" s="3">
         <v>3</v>
@@ -981,7 +981,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C31" s="3">
         <v>1</v>
@@ -995,7 +995,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -1009,7 +1009,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C33" s="3">
         <v>2</v>
@@ -1023,7 +1023,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C34" s="3">
         <v>2</v>
@@ -1037,7 +1037,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C35" s="3">
         <v>3</v>
@@ -1051,7 +1051,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C36" s="3">
         <v>3</v>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F33439-B736-400F-B45D-89AB7A7326C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783ADAD2-FA79-4068-948A-1018BF6391DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -133,59 +133,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>최지원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>까밀라</t>
-  </si>
-  <si>
-    <t>남1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남3.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남3.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여2.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여2.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여3.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이휘영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>까미게스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박수현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수현남편님</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김예진</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -251,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -259,12 +207,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,10 +493,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.25" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="3" customWidth="1"/>
     <col min="3" max="4" width="36.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -813,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="2">
         <v>1.5</v>
@@ -875,188 +819,6 @@
         <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="3">
-        <v>1</v>
-      </c>
-      <c r="D25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="3">
-        <v>1</v>
-      </c>
-      <c r="D26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="3">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="3">
-        <v>2</v>
-      </c>
-      <c r="D28" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="3">
-        <v>3</v>
-      </c>
-      <c r="D29" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="3">
-        <v>3</v>
-      </c>
-      <c r="D30" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="3">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="5">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="3">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="3">
-        <v>2</v>
-      </c>
-      <c r="D33" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="3">
-        <v>2</v>
-      </c>
-      <c r="D34" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="5">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="3">
-        <v>3</v>
-      </c>
-      <c r="D36" s="2">
         <v>2</v>
       </c>
     </row>

--- a/dataset/roster.xlsx
+++ b/dataset/roster.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783ADAD2-FA79-4068-948A-1018BF6391DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B7890F-4BE4-48B6-93DC-0C656BB2DD7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15550" yWindow="-16110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="465" windowWidth="22905" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -134,6 +134,14 @@
   </si>
   <si>
     <t>까밀라</t>
+  </si>
+  <si>
+    <t>박연규</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김예진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -172,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -195,11 +203,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -208,6 +227,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -493,7 +518,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.25" style="3" customWidth="1"/>
@@ -746,7 +771,7 @@
         <v>21</v>
       </c>
       <c r="C18" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -760,7 +785,7 @@
         <v>25</v>
       </c>
       <c r="C19" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2">
         <v>2</v>
@@ -774,7 +799,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -819,6 +844,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="D25" s="5">
         <v>2</v>
       </c>
     </row>
